--- a/agenda.xlsx
+++ b/agenda.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="工作坊議程" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,6 +427,11 @@
   </sheetPr>
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/agenda.xlsx
+++ b/agenda.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,10 +43,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -57,8 +62,8 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -428,174 +433,233 @@
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>時間</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>內容</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>講者</t>
+          <t>Speaker</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>時間：09:00~09:30，內容：報到，講者：無</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>09:00-09:30</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>報到</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>時間：09:30~09:40，內容：開場致詞，講者：王教授</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>09:30-09:40</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>開場致詞</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>王教授</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>時間：09:40~10:05，內容：邁向6G</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>的AI-RAN及O-RAN</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>趨勢介紹，講者：劉教授</t>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>09:40-10:05</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>邁向 6G 的 AI-RAN 及 O-RAN 趨勢介紹</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>劉教授</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>時間：10:05~10:30，內容：下世代B5G/6G專網應用與未來趨勢，講者：陳教授</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>10:05-10:30</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>下世代 B5G/6G 專網應用與未來趨勢</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>陳教授</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>時間：10:30~10:50，內容：Break，講者：無</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>時間：10:50~11:20，內容：從O-RAN到AI-RAN</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>智慧通訊的節能應用，講者：教學團隊</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>10:30-10:50</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n"/>
+    </row>
+    <row r="7" ht="35" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10:50-11:20</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>從 O-RAN 到 AI-RAN
+智慧通訊的節能應用</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>教學團隊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>時間：11:20~12:00，內容：O-RAN環境和各模組化功能介紹，講者：教學團隊</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>11:20-12:00</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>O-RAN 環境和各模組化功能介紹</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>時間：12:00~13:30，內容：Lunch，講者：無</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>12:00-13:30</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>時間：13:30~14:00，內容：O-RAN</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>的市場應用案例，講者：教學團隊</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>13:30-14:00</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>O-RAN 的市場應用案例</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>教學團隊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>時間：14:00~14:30，內容：O-RAN</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>OSC環境建置教學，講者：教學團隊</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>14:00-14:30</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>O-RAN OSC 環境建置教學</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>時間：14:30~14:50，內容：Break，講者：無</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>時間：14:50~15:50，內容：O-RAN</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>OSC第三方應用程式</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>xApps建置教學，講者：教學團隊</t>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>14:30-14:50</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="n"/>
+    </row>
+    <row r="13" ht="35" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>14:50-15:50</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>O-RAN OSC 第三方應用程式
+xApps 建置教學</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>教學團隊</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>時間：15:50~16:30，內容：現場討論時間，講者：教學團隊</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>15:50-16:30</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>現場討論時間</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="B12:C12"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/agenda.xlsx
+++ b/agenda.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>邁向 6G 的 AI-RAN 及 O-RAN 趨勢介紹</t>
+          <t>從 MWC 2026 到 6G：AI-RAN 標準、開源與互通測試的最新進展</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>下世代 B5G/6G 專網應用與未來趨勢</t>
+          <t>基於 O-RAN 開放介面的 ISAC 無線感知技術</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -540,8 +540,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>從 O-RAN 到 AI-RAN
-智慧通訊的節能應用</t>
+          <t>Federated Foundational Models in AI-RAN：Practical and Forward Looking Perspective</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
@@ -558,7 +557,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>O-RAN 環境和各模組化功能介紹</t>
+          <t>O-RAN 環境與各模組化功能介紹</t>
         </is>
       </c>
       <c r="C8" s="1" t="n"/>
@@ -584,7 +583,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>O-RAN 的市場應用案例</t>
+          <t>O-RAN 開源軟體組織簡介</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -601,7 +600,7 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>O-RAN OSC 環境建置教學</t>
+          <t>O-RAN 實驗環境建置教學</t>
         </is>
       </c>
       <c r="C11" s="1" t="n"/>
@@ -627,8 +626,7 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>O-RAN OSC 第三方應用程式
-xApps 建置教學</t>
+          <t>O-RAN xApps 實作建置教學</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
